--- a/database/event/4370/event_4370_evp_summary.xlsx
+++ b/database/event/4370/event_4370_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.2896</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0757</v>
+        <v>1.0325</v>
       </c>
       <c r="E2" t="n">
         <v>3.7059</v>
@@ -548,7 +548,7 @@
         <v>0.2193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7126</v>
+        <v>0.6744</v>
       </c>
       <c r="E3" t="n">
         <v>2.8069</v>
@@ -594,7 +594,7 @@
         <v>0.2179</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7053</v>
+        <v>0.6672</v>
       </c>
       <c r="E4" t="n">
         <v>2.789</v>
@@ -640,7 +640,7 @@
         <v>0.2123</v>
       </c>
       <c r="D5" t="n">
-        <v>0.676</v>
+        <v>0.6383</v>
       </c>
       <c r="E5" t="n">
         <v>2.7165</v>
@@ -686,7 +686,7 @@
         <v>0.1962</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5929</v>
+        <v>0.5564</v>
       </c>
       <c r="E6" t="n">
         <v>2.5108</v>
@@ -732,7 +732,7 @@
         <v>0.1956</v>
       </c>
       <c r="D7" t="n">
-        <v>0.59</v>
+        <v>0.5534</v>
       </c>
       <c r="E7" t="n">
         <v>2.5034</v>
@@ -778,7 +778,7 @@
         <v>0.1877</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5491</v>
+        <v>0.5132</v>
       </c>
       <c r="E8" t="n">
         <v>2.4023</v>
@@ -824,7 +824,7 @@
         <v>0.186</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5402</v>
+        <v>0.5044</v>
       </c>
       <c r="E9" t="n">
         <v>2.3802</v>
@@ -870,7 +870,7 @@
         <v>0.1693</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4539</v>
+        <v>0.4192</v>
       </c>
       <c r="E10" t="n">
         <v>2.1665</v>
@@ -916,7 +916,7 @@
         <v>0.0878</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0325</v>
+        <v>0.0037</v>
       </c>
       <c r="E11" t="n">
         <v>1.1234</v>
@@ -962,7 +962,7 @@
         <v>0.0474</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1764</v>
+        <v>-0.2023</v>
       </c>
       <c r="E12" t="n">
         <v>0.6064000000000001</v>
@@ -1008,7 +1008,7 @@
         <v>0.0387</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2214</v>
+        <v>-0.2467</v>
       </c>
       <c r="E13" t="n">
         <v>0.4951</v>
@@ -1054,7 +1054,7 @@
         <v>-0.008200000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4639</v>
+        <v>-0.4858</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1052</v>
@@ -1100,7 +1100,7 @@
         <v>-0.0358</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6067</v>
+        <v>-0.6267</v>
       </c>
       <c r="E15" t="n">
         <v>-0.4587</v>
@@ -1146,7 +1146,7 @@
         <v>-0.0475</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6859</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6075</v>
@@ -1192,7 +1192,7 @@
         <v>-0.08790000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8756</v>
+        <v>-0.8919</v>
       </c>
       <c r="E17" t="n">
         <v>-1.1245</v>
@@ -1238,7 +1238,7 @@
         <v>-0.1058</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.9832</v>
       </c>
       <c r="E18" t="n">
         <v>-1.3537</v>
@@ -1284,7 +1284,7 @@
         <v>-0.1216</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0498</v>
+        <v>-1.0637</v>
       </c>
       <c r="E19" t="n">
         <v>-1.5557</v>
@@ -1330,7 +1330,7 @@
         <v>-0.1542</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2185</v>
+        <v>-1.23</v>
       </c>
       <c r="E20" t="n">
         <v>-1.9731</v>
@@ -1376,7 +1376,7 @@
         <v>-0.1691</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2954</v>
+        <v>-1.3059</v>
       </c>
       <c r="E21" t="n">
         <v>-2.1636</v>

--- a/database/event/4370/event_4370_evp_summary.xlsx
+++ b/database/event/4370/event_4370_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.7059</v>
+        <v>3.9989</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2896</v>
+        <v>0.3125</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0325</v>
+        <v>1.1673</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7059</v>
+        <v>3.9989</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9086</v>
+        <v>2.2467</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2027</v>
+        <v>1.7522</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9086</v>
+        <v>2.4298</v>
       </c>
       <c r="I2" t="n">
-        <v>3.168</v>
+        <v>1.2634</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2027</v>
+        <v>1.7522</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9653</v>
+        <v>3.0156</v>
       </c>
       <c r="N2" t="n">
         <v>273</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.8069</v>
+        <v>3.6541</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2193</v>
+        <v>0.2855</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6744</v>
+        <v>1.0116</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8069</v>
+        <v>3.6541</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5651</v>
+        <v>3.5057</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7582</v>
+        <v>0.1484</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5651</v>
+        <v>6.8654</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8896</v>
+        <v>3.5697</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7582</v>
+        <v>0.1484</v>
       </c>
       <c r="K3" t="n">
         <v>132</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>2.1314</v>
+        <v>3.7181</v>
       </c>
       <c r="N3" t="n">
         <v>273</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.789</v>
+        <v>3.6165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2179</v>
+        <v>0.2826</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6672</v>
+        <v>0.9947</v>
       </c>
       <c r="E4" t="n">
-        <v>2.789</v>
+        <v>3.6165</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1586</v>
+        <v>2.3755</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6304</v>
+        <v>1.241</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1586</v>
+        <v>2.8833</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9391</v>
+        <v>1.4992</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6304</v>
+        <v>1.241</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5695</v>
+        <v>2.7402</v>
       </c>
       <c r="N4" t="n">
         <v>273</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7165</v>
+        <v>3.0956</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2123</v>
+        <v>0.2419</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6383</v>
+        <v>0.7595</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7165</v>
+        <v>3.0956</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5626</v>
+        <v>2.4933</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1539</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5626</v>
+        <v>3.2984</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2665</v>
+        <v>1.715</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1539</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4204</v>
+        <v>2.3173</v>
       </c>
       <c r="N5" t="n">
-        <v>273</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5108</v>
+        <v>3.073</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1962</v>
+        <v>0.2401</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5564</v>
+        <v>0.7493</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5108</v>
+        <v>3.073</v>
       </c>
       <c r="F6" t="n">
-        <v>1.165</v>
+        <v>1.7673</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3458</v>
+        <v>1.3057</v>
       </c>
       <c r="H6" t="n">
-        <v>1.165</v>
+        <v>1.7673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9443</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3458</v>
+        <v>1.3057</v>
       </c>
       <c r="K6" t="n">
         <v>60</v>
@@ -713,7 +713,7 @@
         <v>141</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2901</v>
+        <v>2.2246</v>
       </c>
       <c r="N6" t="n">
         <v>201</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5034</v>
+        <v>2.975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1956</v>
+        <v>0.2325</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5534</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5034</v>
+        <v>2.975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0818</v>
+        <v>1.8767</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4216</v>
+        <v>1.0983</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0818</v>
+        <v>1.8767</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0663</v>
+        <v>0.9758</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4216</v>
+        <v>1.0983</v>
       </c>
       <c r="K7" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4879</v>
+        <v>2.0741</v>
       </c>
       <c r="N7" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4023</v>
+        <v>2.9581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1877</v>
+        <v>0.2311</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5132</v>
+        <v>0.6974</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4023</v>
+        <v>2.9581</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1395</v>
+        <v>2.2017</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2628</v>
+        <v>0.7564</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1395</v>
+        <v>2.271</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7341</v>
+        <v>1.1808</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2628</v>
+        <v>0.7564</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="L8" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9969</v>
+        <v>1.9372</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3802</v>
+        <v>2.6586</v>
       </c>
       <c r="C9" t="n">
-        <v>0.186</v>
+        <v>0.2077</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5044</v>
+        <v>0.5622</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3802</v>
+        <v>2.6586</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2898</v>
+        <v>3.1298</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0904</v>
+        <v>-0.4712</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2898</v>
+        <v>5.5413</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0454</v>
+        <v>2.8812</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0904</v>
+        <v>-0.4712</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
         <v>141</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1358</v>
+        <v>2.41</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1665</v>
+        <v>2.4495</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1693</v>
+        <v>0.1914</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4192</v>
+        <v>0.4678</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1665</v>
+        <v>2.4495</v>
       </c>
       <c r="F10" t="n">
-        <v>1.413</v>
+        <v>0.5795</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7534999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="H10" t="n">
-        <v>1.413</v>
+        <v>0.5795</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1453</v>
+        <v>0.3013</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7534999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8988</v>
+        <v>2.1713</v>
       </c>
       <c r="N10" t="n">
         <v>197</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1234</v>
+        <v>1.655</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0878</v>
+        <v>0.1293</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0037</v>
+        <v>0.1091</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1234</v>
+        <v>1.655</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1166</v>
+        <v>2.3681</v>
       </c>
       <c r="G11" t="n">
-        <v>1.24</v>
+        <v>-0.7131</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1166</v>
+        <v>2.8576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0945</v>
+        <v>1.4858</v>
       </c>
       <c r="J11" t="n">
-        <v>1.24</v>
+        <v>-0.7131</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1455</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>197</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6064000000000001</v>
+        <v>1.5654</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0474</v>
+        <v>0.1223</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2023</v>
+        <v>0.0687</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6064000000000001</v>
+        <v>1.5654</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4022</v>
+        <v>0.5258</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7958</v>
+        <v>1.0396</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4022</v>
+        <v>0.5258</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1365</v>
+        <v>0.2734</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7958</v>
+        <v>1.0396</v>
       </c>
       <c r="K12" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3407000000000001</v>
+        <v>1.313</v>
       </c>
       <c r="N12" t="n">
-        <v>273</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4951</v>
+        <v>0.5693</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0387</v>
+        <v>0.0445</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2467</v>
+        <v>-0.381</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4951</v>
+        <v>0.5693</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0711</v>
+        <v>0.0564</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5662</v>
+        <v>0.5129</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0711</v>
+        <v>0.0564</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0576</v>
+        <v>0.0293</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5662</v>
+        <v>0.5129</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5422</v>
       </c>
       <c r="N13" t="n">
         <v>97</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1052</v>
+        <v>0.3017</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0236</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4858</v>
+        <v>-0.5018</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1052</v>
+        <v>0.3017</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9253</v>
+        <v>-0.4933</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9253</v>
+        <v>-0.4933</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.75</v>
+        <v>-0.2565</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="K14" t="n">
         <v>146</v>
@@ -1081,7 +1081,7 @@
         <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07010000000000005</v>
+        <v>0.5385</v>
       </c>
       <c r="N14" t="n">
         <v>197</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4587</v>
+        <v>-0.2031</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0358</v>
+        <v>-0.0159</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6267</v>
+        <v>-0.7297</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4587</v>
+        <v>-0.2031</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7723</v>
+        <v>0.4835</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3136</v>
+        <v>-0.6866</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7723</v>
+        <v>0.4835</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.626</v>
+        <v>0.2514</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3136</v>
+        <v>-0.6866</v>
       </c>
       <c r="K15" t="n">
         <v>46</v>
@@ -1127,7 +1127,7 @@
         <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3124</v>
+        <v>-0.4352</v>
       </c>
       <c r="N15" t="n">
         <v>97</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.6075</v>
+        <v>-0.4446</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0475</v>
+        <v>-0.0347</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6859</v>
+        <v>-0.8387</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6075</v>
+        <v>-0.4446</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2338</v>
+        <v>-0.8016</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6263</v>
+        <v>0.357</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2338</v>
+        <v>-0.8016</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>-0.4168</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6263</v>
+        <v>0.357</v>
       </c>
       <c r="K16" t="n">
         <v>46</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3737</v>
+        <v>-0.05980000000000002</v>
       </c>
       <c r="N16" t="n">
         <v>97</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.1245</v>
+        <v>-1.2602</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0985</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8919</v>
+        <v>-1.2069</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1245</v>
+        <v>-1.2602</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1245</v>
+        <v>-1.9232</v>
       </c>
       <c r="G17" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1.9232</v>
+      </c>
+      <c r="I17" t="n">
         <v>-1</v>
       </c>
-      <c r="H17" t="n">
-        <v>-0.1245</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.1009</v>
-      </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0.663</v>
       </c>
       <c r="K17" t="n">
         <v>46</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1009</v>
+        <v>-0.337</v>
       </c>
       <c r="N17" t="n">
         <v>97</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.3537</v>
+        <v>-1.7312</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1058</v>
+        <v>-0.1353</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9832</v>
+        <v>-1.4196</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3537</v>
+        <v>-1.7312</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8642</v>
+        <v>-1.0774</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5105</v>
+        <v>-0.6538</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8642</v>
+        <v>-1.0774</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.511</v>
+        <v>-0.5602</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5105</v>
+        <v>-0.6538</v>
       </c>
       <c r="K18" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="L18" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0005</v>
+        <v>-1.214</v>
       </c>
       <c r="N18" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.5557</v>
+        <v>-2.0171</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1216</v>
+        <v>-0.1576</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0637</v>
+        <v>-1.5486</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5557</v>
+        <v>-2.0171</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.317</v>
+        <v>-1.9165</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2387</v>
+        <v>-0.1006</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.317</v>
+        <v>-1.9165</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0675</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2387</v>
+        <v>-0.1006</v>
       </c>
       <c r="K19" t="n">
         <v>60</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3062</v>
+        <v>-1.0971</v>
       </c>
       <c r="N19" t="n">
         <v>201</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.9731</v>
+        <v>-2.0643</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1542</v>
+        <v>-0.1613</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.23</v>
+        <v>-1.5699</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9731</v>
+        <v>-2.0643</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2329</v>
+        <v>-1.268</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7402</v>
+        <v>-0.7963</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2329</v>
+        <v>-1.268</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9993</v>
+        <v>-0.6593</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7402</v>
+        <v>-0.7963</v>
       </c>
       <c r="K20" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="L20" t="n">
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7395</v>
+        <v>-1.4556</v>
       </c>
       <c r="N20" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.1636</v>
+        <v>-2.2428</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1691</v>
+        <v>-0.1752</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3059</v>
+        <v>-1.6505</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1636</v>
+        <v>-2.2428</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1636</v>
+        <v>-2.7302</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0.4874</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1636</v>
+        <v>-2.7302</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9431</v>
+        <v>-1.4196</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>0.4874</v>
       </c>
       <c r="K21" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9431</v>
+        <v>-0.9321999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>97</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -1509,10 +1509,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9623</v>
+        <v>0.8867</v>
       </c>
       <c r="J2" t="n">
-        <v>18.2837</v>
+        <v>16.8473</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7941</v>
+        <v>0.7284</v>
       </c>
       <c r="J3" t="n">
-        <v>15.0879</v>
+        <v>13.8396</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4919</v>
+        <v>0.4855</v>
       </c>
       <c r="J4" t="n">
-        <v>9.3461</v>
+        <v>9.224500000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.27</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3243</v>
+        <v>0.3412</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1617</v>
+        <v>6.4828</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>1.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1025</v>
+        <v>0.1385</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9475</v>
+        <v>2.6315</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>0.75</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2547</v>
+        <v>-0.2211</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.8393</v>
+        <v>-4.2009</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.66</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3939</v>
+        <v>-0.3148</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.4841</v>
+        <v>-5.9812</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.61</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4756</v>
+        <v>-0.3627</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.0364</v>
+        <v>-6.8913</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5772</v>
+        <v>-0.4064</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.9668</v>
+        <v>-7.7216</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.6148</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.8644</v>
+        <v>-11.6812</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4399</v>
+        <v>0.5113</v>
       </c>
       <c r="J12" t="n">
-        <v>12.3172</v>
+        <v>14.3164</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3691</v>
+        <v>0.4203</v>
       </c>
       <c r="J13" t="n">
-        <v>10.3348</v>
+        <v>11.7684</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2279</v>
+        <v>0.2464</v>
       </c>
       <c r="J14" t="n">
-        <v>6.3812</v>
+        <v>6.8992</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1354</v>
+        <v>-0.0759</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7912</v>
+        <v>-2.1252</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7407</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.7396</v>
+        <v>-14.042</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3098</v>
+        <v>1.1938</v>
       </c>
       <c r="J17" t="n">
-        <v>36.6744</v>
+        <v>33.4264</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3423</v>
+        <v>0.3489</v>
       </c>
       <c r="J18" t="n">
-        <v>9.5844</v>
+        <v>9.7692</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6936</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2593</v>
+        <v>-0.1925</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.2604</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4447</v>
+        <v>-0.3789</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.4516</v>
+        <v>-10.6092</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.245</v>
+        <v>0.2436</v>
       </c>
       <c r="J22" t="n">
-        <v>6.125</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.93</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0766</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.915</v>
+        <v>-1.9925</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1315</v>
+        <v>-0.115</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2875</v>
+        <v>-2.875</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.64</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5603</v>
+        <v>-0.3704</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.0075</v>
+        <v>-9.26</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6516</v>
+        <v>-0.4357</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.29</v>
+        <v>-10.8925</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>2.11</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1295</v>
+        <v>1.8664</v>
       </c>
       <c r="J27" t="n">
-        <v>53.2375</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2444</v>
+        <v>0.3202</v>
       </c>
       <c r="J28" t="n">
-        <v>6.11</v>
+        <v>8.005000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1285</v>
+        <v>0.2043</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2125</v>
+        <v>5.1075</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0388</v>
+        <v>0.0365</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.97</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4609</v>
+        <v>-0.385</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.5225</v>
+        <v>-9.625</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9865</v>
+        <v>0.9666</v>
       </c>
       <c r="J32" t="n">
-        <v>29.595</v>
+        <v>28.998</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7356</v>
+        <v>0.7096</v>
       </c>
       <c r="J33" t="n">
-        <v>22.068</v>
+        <v>21.288</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.105</v>
+        <v>0.1458</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2171</v>
+        <v>-0.1538</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.513</v>
+        <v>-4.614</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.84</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6005</v>
+        <v>-0.542</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.015</v>
+        <v>-16.26</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3956</v>
+        <v>0.4503</v>
       </c>
       <c r="J37" t="n">
-        <v>11.868</v>
+        <v>13.509</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0232</v>
+        <v>0.005</v>
       </c>
       <c r="J38" t="n">
-        <v>0.696</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.998</v>
+        <v>-1.428</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2335</v>
+        <v>-0.1415</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.005</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4184</v>
+        <v>-0.2647</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.552</v>
+        <v>-7.941</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5736</v>
+        <v>0.5269</v>
       </c>
       <c r="J42" t="n">
-        <v>17.208</v>
+        <v>15.807</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2129</v>
+        <v>0.1739</v>
       </c>
       <c r="J43" t="n">
-        <v>6.387</v>
+        <v>5.217</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1906</v>
+        <v>-0.111</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.718</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2917</v>
+        <v>-0.1768</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.750999999999999</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4387</v>
+        <v>-0.2779</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.161</v>
+        <v>-8.337</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3516</v>
+        <v>0.289</v>
       </c>
       <c r="J47" t="n">
-        <v>10.548</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3367</v>
+        <v>0.276</v>
       </c>
       <c r="J48" t="n">
-        <v>10.101</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1896</v>
+        <v>0.1533</v>
       </c>
       <c r="J49" t="n">
-        <v>5.688</v>
+        <v>4.599</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2254</v>
+        <v>-0.1285</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.762</v>
+        <v>-3.855</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2748</v>
+        <v>-0.1617</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.244</v>
+        <v>-4.851</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9524</v>
+        <v>0.959</v>
       </c>
       <c r="J52" t="n">
-        <v>24.7624</v>
+        <v>24.934</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7612</v>
       </c>
       <c r="J53" t="n">
-        <v>19.357</v>
+        <v>19.7912</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5175</v>
+        <v>0.5782</v>
       </c>
       <c r="J54" t="n">
-        <v>13.455</v>
+        <v>15.0332</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4904</v>
+        <v>0.5542</v>
       </c>
       <c r="J55" t="n">
-        <v>12.7504</v>
+        <v>14.4092</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.247</v>
+        <v>0.3216</v>
       </c>
       <c r="J56" t="n">
-        <v>6.422</v>
+        <v>8.361599999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3197</v>
+        <v>0.342</v>
       </c>
       <c r="J57" t="n">
-        <v>8.312200000000001</v>
+        <v>8.891999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0683</v>
+        <v>-0.0716</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.7758</v>
+        <v>-1.8616</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2629</v>
+        <v>-0.1809</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.8354</v>
+        <v>-4.7034</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4273</v>
+        <v>-0.2786</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.1098</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6313</v>
+        <v>-0.4204</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.4138</v>
+        <v>-10.9304</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.342</v>
+        <v>1.2155</v>
       </c>
       <c r="J62" t="n">
-        <v>40.26</v>
+        <v>36.465</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3813</v>
+        <v>0.3277</v>
       </c>
       <c r="J63" t="n">
-        <v>11.439</v>
+        <v>9.831</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0864</v>
+        <v>-0.0898</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.592</v>
+        <v>-2.694</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.7</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8981</v>
+        <v>-0.8673</v>
       </c>
       <c r="J65" t="n">
-        <v>-26.943</v>
+        <v>-26.019</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0753</v>
+        <v>-1.0616</v>
       </c>
       <c r="J66" t="n">
-        <v>-32.259</v>
+        <v>-31.848</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4259</v>
+        <v>0.5104</v>
       </c>
       <c r="J67" t="n">
-        <v>12.777</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3247</v>
+        <v>0.3893</v>
       </c>
       <c r="J68" t="n">
-        <v>9.741</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2772</v>
+        <v>0.3358</v>
       </c>
       <c r="J69" t="n">
-        <v>8.316000000000001</v>
+        <v>10.074</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1443</v>
+        <v>0.2057</v>
       </c>
       <c r="J70" t="n">
-        <v>4.329</v>
+        <v>6.171</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2263</v>
+        <v>-0.1249</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.789</v>
+        <v>-3.747</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0307</v>
+        <v>1.0087</v>
       </c>
       <c r="J72" t="n">
-        <v>30.921</v>
+        <v>30.261</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6641</v>
+        <v>0.6481</v>
       </c>
       <c r="J73" t="n">
-        <v>19.923</v>
+        <v>19.443</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5061</v>
+        <v>0.4995</v>
       </c>
       <c r="J74" t="n">
-        <v>15.183</v>
+        <v>14.985</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0078</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>0.234</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6129</v>
+        <v>-0.5523</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.387</v>
+        <v>-16.569</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5808</v>
+        <v>0.6977</v>
       </c>
       <c r="J77" t="n">
-        <v>17.424</v>
+        <v>20.931</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1892</v>
+        <v>0.1773</v>
       </c>
       <c r="J78" t="n">
-        <v>5.676</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4489</v>
+        <v>-0.2912</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.467</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5716</v>
+        <v>-0.3767</v>
       </c>
       <c r="J80" t="n">
-        <v>-17.148</v>
+        <v>-11.301</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6105</v>
+        <v>-0.4047</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.315</v>
+        <v>-12.141</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0052</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>28.1456</v>
+        <v>27.4484</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7791</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>21.8148</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2359</v>
+        <v>-0.1795</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.6052</v>
+        <v>-5.026</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5089</v>
+        <v>-0.4505</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.2492</v>
+        <v>-12.614</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5883</v>
+        <v>-0.5325</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.4724</v>
+        <v>-14.91</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6317</v>
+        <v>0.7684</v>
       </c>
       <c r="J87" t="n">
-        <v>17.6876</v>
+        <v>21.5152</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2912</v>
+        <v>0.3241</v>
       </c>
       <c r="J88" t="n">
-        <v>8.153600000000001</v>
+        <v>9.0748</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0891</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>2.4948</v>
+        <v>2.5424</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2951</v>
+        <v>-0.1782</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.2628</v>
+        <v>-4.9896</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6345</v>
+        <v>-0.4207</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.766</v>
+        <v>-11.7796</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>2.34</v>
       </c>
       <c r="I92" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J92" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.62</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2485</v>
+        <v>1.2214</v>
       </c>
       <c r="J93" t="n">
-        <v>22.473</v>
+        <v>21.9852</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>1.42</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8272</v>
+        <v>0.9706</v>
       </c>
       <c r="J94" t="n">
-        <v>14.8896</v>
+        <v>17.4708</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>12.6738</v>
+        <v>15.2514</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6834</v>
+        <v>0.8254</v>
       </c>
       <c r="J96" t="n">
-        <v>12.3012</v>
+        <v>14.8572</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.3488</v>
+        <v>-0.2948</v>
       </c>
       <c r="J97" t="n">
-        <v>-6.2784</v>
+        <v>-5.3064</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>0.45</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.648</v>
+        <v>-0.4811</v>
       </c>
       <c r="J98" t="n">
-        <v>-11.664</v>
+        <v>-8.659800000000001</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.42</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.7151</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>-12.8718</v>
+        <v>-9.136799999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.41</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7326</v>
+        <v>-0.517</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.1868</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.33</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.596</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.4332</v>
+        <v>-10.728</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8561</v>
+        <v>0.6279</v>
       </c>
       <c r="J102" t="n">
-        <v>24.8269</v>
+        <v>18.2091</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.715</v>
+        <v>0.5421</v>
       </c>
       <c r="J103" t="n">
-        <v>20.735</v>
+        <v>15.7209</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4818</v>
+        <v>0.4078</v>
       </c>
       <c r="J104" t="n">
-        <v>13.9722</v>
+        <v>11.8262</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2951</v>
+        <v>0.2975</v>
       </c>
       <c r="J105" t="n">
-        <v>8.5579</v>
+        <v>8.6275</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.0382</v>
+        <v>-1.0184</v>
       </c>
       <c r="J106" t="n">
-        <v>-30.1078</v>
+        <v>-29.5336</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5955</v>
+        <v>0.5634</v>
       </c>
       <c r="J107" t="n">
-        <v>17.2695</v>
+        <v>16.3386</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5955</v>
+        <v>0.5634</v>
       </c>
       <c r="J108" t="n">
-        <v>17.2695</v>
+        <v>16.3386</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2118</v>
+        <v>0.2498</v>
       </c>
       <c r="J109" t="n">
-        <v>6.1422</v>
+        <v>7.2442</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3427</v>
+        <v>-0.2073</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.9383</v>
+        <v>-6.0117</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5461</v>
+        <v>-0.3541</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.8369</v>
+        <v>-10.2689</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.83</v>
       </c>
       <c r="I112" t="n">
-        <v>1.7539</v>
+        <v>1.2423</v>
       </c>
       <c r="J112" t="n">
-        <v>38.5858</v>
+        <v>27.3306</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.525</v>
+        <v>0.4975</v>
       </c>
       <c r="J113" t="n">
-        <v>11.55</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.525</v>
+        <v>0.4975</v>
       </c>
       <c r="J114" t="n">
-        <v>11.55</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.298</v>
+        <v>0.3646</v>
       </c>
       <c r="J115" t="n">
-        <v>6.556</v>
+        <v>8.0212</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2717</v>
+        <v>0.3486</v>
       </c>
       <c r="J116" t="n">
-        <v>5.9774</v>
+        <v>7.6692</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4145</v>
+        <v>0.4132</v>
       </c>
       <c r="J117" t="n">
-        <v>9.119</v>
+        <v>9.090400000000001</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0293</v>
+        <v>-0.0505</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.6446</v>
+        <v>-1.111</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2819</v>
+        <v>-0.2064</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.2018</v>
+        <v>-4.5408</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6599</v>
+        <v>-0.4422</v>
       </c>
       <c r="J120" t="n">
-        <v>-14.5178</v>
+        <v>-9.728400000000001</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7103</v>
+        <v>-0.4793</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.6266</v>
+        <v>-10.5446</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2827</v>
+        <v>0.3098</v>
       </c>
       <c r="J122" t="n">
-        <v>9.611800000000001</v>
+        <v>10.5332</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J123" t="n">
-        <v>4.811</v>
+        <v>4.8348</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J124" t="n">
-        <v>4.811</v>
+        <v>4.8348</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0592</v>
+        <v>-0.0349</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.0128</v>
+        <v>-1.1866</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4913</v>
+        <v>-0.3156</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.7042</v>
+        <v>-10.7304</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8964</v>
+        <v>0.6579</v>
       </c>
       <c r="J127" t="n">
-        <v>30.4776</v>
+        <v>22.3686</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7341</v>
+        <v>0.5606</v>
       </c>
       <c r="J128" t="n">
-        <v>24.9594</v>
+        <v>19.0604</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1471</v>
+        <v>0.1997</v>
       </c>
       <c r="J129" t="n">
-        <v>5.0014</v>
+        <v>6.7898</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J130" t="n">
-        <v>2.6996</v>
+        <v>4.5934</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1564</v>
+        <v>-0.0871</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.3176</v>
+        <v>-2.9614</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4732</v>
+        <v>0.4653</v>
       </c>
       <c r="J132" t="n">
-        <v>16.562</v>
+        <v>16.2855</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.301</v>
+        <v>0.3345</v>
       </c>
       <c r="J133" t="n">
-        <v>10.535</v>
+        <v>11.7075</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0497</v>
+        <v>0.0634</v>
       </c>
       <c r="J134" t="n">
-        <v>1.7395</v>
+        <v>2.219</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0785</v>
+        <v>-0.0379</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.7475</v>
+        <v>-1.3265</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.537</v>
+        <v>-0.3481</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.795</v>
+        <v>-12.1835</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7045</v>
+        <v>0.5241</v>
       </c>
       <c r="J137" t="n">
-        <v>24.6575</v>
+        <v>18.3435</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0272</v>
+        <v>0.0036</v>
       </c>
       <c r="J138" t="n">
-        <v>0.952</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1823</v>
+        <v>-0.1597</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.3805</v>
+        <v>-5.5895</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2558</v>
+        <v>-0.2238</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.952999999999999</v>
+        <v>-7.833</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6843</v>
+        <v>-0.641</v>
       </c>
       <c r="J141" t="n">
-        <v>-23.9505</v>
+        <v>-22.435</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4370/event_4370_evp_summary.xlsx
+++ b/database/event/4370/event_4370_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.9989</v>
+        <v>3.9268</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3125</v>
+        <v>0.3068</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1673</v>
+        <v>1.1634</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9989</v>
+        <v>3.9268</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2467</v>
+        <v>2.1647</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7522</v>
+        <v>1.7621</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4298</v>
+        <v>2.248</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2634</v>
+        <v>1.2139</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7522</v>
+        <v>1.7621</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0156</v>
+        <v>2.976</v>
       </c>
       <c r="N2" t="n">
         <v>273</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6541</v>
+        <v>3.5543</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2855</v>
+        <v>0.2777</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0116</v>
+        <v>0.9938</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6541</v>
+        <v>3.5543</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5057</v>
+        <v>2.2865</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1484</v>
+        <v>1.2678</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8654</v>
+        <v>2.6499</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5697</v>
+        <v>1.4309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1484</v>
+        <v>1.2678</v>
       </c>
       <c r="K3" t="n">
         <v>132</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7181</v>
+        <v>2.6987</v>
       </c>
       <c r="N3" t="n">
         <v>273</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6165</v>
+        <v>3.5168</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2826</v>
+        <v>0.2748</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9947</v>
+        <v>0.9767</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6165</v>
+        <v>3.5168</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3755</v>
+        <v>3.3862</v>
       </c>
       <c r="G4" t="n">
-        <v>1.241</v>
+        <v>0.1306</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8833</v>
+        <v>6.2781</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4992</v>
+        <v>3.3901</v>
       </c>
       <c r="J4" t="n">
-        <v>1.241</v>
+        <v>0.1306</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7402</v>
+        <v>3.5207</v>
       </c>
       <c r="N4" t="n">
         <v>273</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0956</v>
+        <v>3.0141</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2419</v>
+        <v>0.2355</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7595</v>
+        <v>0.7479</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0956</v>
+        <v>3.0141</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4933</v>
+        <v>2.4137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6004</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2984</v>
+        <v>3.0695</v>
       </c>
       <c r="I5" t="n">
-        <v>1.715</v>
+        <v>1.6575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6004</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3173</v>
+        <v>2.2579</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.073</v>
+        <v>2.9563</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2401</v>
+        <v>0.231</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7493</v>
+        <v>0.7216</v>
       </c>
       <c r="E6" t="n">
-        <v>3.073</v>
+        <v>2.9563</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7673</v>
+        <v>2.1439</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3057</v>
+        <v>0.8124</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7673</v>
+        <v>2.1795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9189000000000001</v>
+        <v>1.1769</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3057</v>
+        <v>0.8124</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="L6" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2246</v>
+        <v>1.9893</v>
       </c>
       <c r="N6" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.975</v>
+        <v>2.9431</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2325</v>
+        <v>0.23</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.7156</v>
       </c>
       <c r="E7" t="n">
-        <v>2.975</v>
+        <v>2.9431</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8767</v>
+        <v>1.5769</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0983</v>
+        <v>1.3662</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8767</v>
+        <v>1.5769</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9758</v>
+        <v>0.8515</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0983</v>
+        <v>1.3662</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
@@ -759,7 +759,7 @@
         <v>141</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0741</v>
+        <v>2.2177</v>
       </c>
       <c r="N7" t="n">
         <v>201</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9581</v>
+        <v>2.8784</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2311</v>
+        <v>0.2249</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6974</v>
+        <v>0.6861</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9581</v>
+        <v>2.8784</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2017</v>
+        <v>1.743</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7564</v>
+        <v>1.1354</v>
       </c>
       <c r="H8" t="n">
-        <v>2.271</v>
+        <v>1.743</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1808</v>
+        <v>0.9412</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7564</v>
+        <v>1.1354</v>
       </c>
       <c r="K8" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9372</v>
+        <v>2.0766</v>
       </c>
       <c r="N8" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6586</v>
+        <v>2.7052</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2077</v>
+        <v>0.2114</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5622</v>
+        <v>0.6073</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6586</v>
+        <v>2.7052</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1298</v>
+        <v>3.1525</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4712</v>
+        <v>-0.4473</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5413</v>
+        <v>5.5069</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8812</v>
+        <v>2.9737</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4712</v>
+        <v>-0.4473</v>
       </c>
       <c r="K9" t="n">
         <v>132</v>
@@ -851,7 +851,7 @@
         <v>141</v>
       </c>
       <c r="M9" t="n">
-        <v>2.41</v>
+        <v>2.5264</v>
       </c>
       <c r="N9" t="n">
         <v>273</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4495</v>
+        <v>2.6127</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1914</v>
+        <v>0.2041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4678</v>
+        <v>0.5652</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4495</v>
+        <v>2.6127</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5795</v>
+        <v>0.5637</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87</v>
+        <v>2.0489</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5795</v>
+        <v>0.5637</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3013</v>
+        <v>0.3044</v>
       </c>
       <c r="J10" t="n">
-        <v>1.87</v>
+        <v>2.0489</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1713</v>
+        <v>2.3533</v>
       </c>
       <c r="N10" t="n">
         <v>197</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.655</v>
+        <v>1.5645</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1293</v>
+        <v>0.1222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1091</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.655</v>
+        <v>1.5645</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3681</v>
+        <v>2.2686</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7131</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8576</v>
+        <v>2.5908</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4858</v>
+        <v>1.399</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7131</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>141</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.6949000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>273</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5654</v>
+        <v>1.5288</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1223</v>
+        <v>0.1195</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0687</v>
+        <v>0.0717</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5654</v>
+        <v>1.5288</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5258</v>
+        <v>0.3774</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0396</v>
+        <v>1.1514</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5258</v>
+        <v>0.3774</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2734</v>
+        <v>0.2038</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0396</v>
+        <v>1.1514</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.313</v>
+        <v>1.3552</v>
       </c>
       <c r="N12" t="n">
         <v>197</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5693</v>
+        <v>0.5631</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0445</v>
+        <v>0.044</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.381</v>
+        <v>-0.3679</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5693</v>
+        <v>0.5631</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0564</v>
+        <v>-0.0011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5129</v>
+        <v>0.5642</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0564</v>
+        <v>-0.0011</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0293</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5129</v>
+        <v>0.5642</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5422</v>
+        <v>0.5636</v>
       </c>
       <c r="N13" t="n">
         <v>97</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3017</v>
+        <v>0.2777</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0236</v>
+        <v>0.0217</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5018</v>
+        <v>-0.4978</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3017</v>
+        <v>0.2777</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4933</v>
+        <v>-0.5769</v>
       </c>
       <c r="G14" t="n">
-        <v>0.795</v>
+        <v>0.8546</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4933</v>
+        <v>-0.5769</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2565</v>
+        <v>-0.3115</v>
       </c>
       <c r="J14" t="n">
-        <v>0.795</v>
+        <v>0.8546</v>
       </c>
       <c r="K14" t="n">
         <v>146</v>
@@ -1081,7 +1081,7 @@
         <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5385</v>
+        <v>0.5431</v>
       </c>
       <c r="N14" t="n">
         <v>197</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2031</v>
+        <v>-0.3351</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0262</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7297</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2031</v>
+        <v>-0.3351</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4835</v>
+        <v>0.3722</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6866</v>
+        <v>-0.7073</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4835</v>
+        <v>0.3722</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2514</v>
+        <v>0.201</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6866</v>
+        <v>-0.7073</v>
       </c>
       <c r="K15" t="n">
         <v>46</v>
@@ -1127,7 +1127,7 @@
         <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4352</v>
+        <v>-0.5063</v>
       </c>
       <c r="N15" t="n">
         <v>97</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4446</v>
+        <v>-0.3821</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0347</v>
+        <v>-0.0299</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8387</v>
+        <v>-0.7981</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4446</v>
+        <v>-0.3821</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8016</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.357</v>
+        <v>0.4057</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8016</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4168</v>
+        <v>-0.4254</v>
       </c>
       <c r="J16" t="n">
-        <v>0.357</v>
+        <v>0.4057</v>
       </c>
       <c r="K16" t="n">
         <v>46</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.05980000000000002</v>
+        <v>-0.0197</v>
       </c>
       <c r="N16" t="n">
         <v>97</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.2602</v>
+        <v>-1.151</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0985</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2069</v>
+        <v>-1.1482</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2602</v>
+        <v>-1.151</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9232</v>
+        <v>-1.8519</v>
       </c>
       <c r="G17" t="n">
-        <v>0.663</v>
+        <v>0.7009</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9232</v>
+        <v>-1.8519</v>
       </c>
       <c r="I17" t="n">
         <v>-1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.663</v>
+        <v>0.7009</v>
       </c>
       <c r="K17" t="n">
         <v>46</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.337</v>
+        <v>-0.2991</v>
       </c>
       <c r="N17" t="n">
         <v>97</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.7312</v>
+        <v>-1.6537</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1353</v>
+        <v>-0.1292</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4196</v>
+        <v>-1.377</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7312</v>
+        <v>-1.6537</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0774</v>
+        <v>-1.1156</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6538</v>
+        <v>-0.5381</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0774</v>
+        <v>-1.1156</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5602</v>
+        <v>-0.6024</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6538</v>
+        <v>-0.5381</v>
       </c>
       <c r="K18" t="n">
         <v>146</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.214</v>
+        <v>-1.1405</v>
       </c>
       <c r="N18" t="n">
         <v>197</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.0171</v>
+        <v>-1.7507</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1576</v>
+        <v>-0.1368</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5486</v>
+        <v>-1.4212</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0171</v>
+        <v>-1.7507</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9165</v>
+        <v>-1.6524</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1006</v>
+        <v>-0.0983</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9165</v>
+        <v>-1.6524</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.8923</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1006</v>
+        <v>-0.0983</v>
       </c>
       <c r="K19" t="n">
         <v>60</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0971</v>
+        <v>-0.9905999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>201</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-2.0643</v>
+        <v>-1.8713</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1613</v>
+        <v>-0.1462</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5699</v>
+        <v>-1.4761</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0643</v>
+        <v>-1.8713</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.268</v>
+        <v>-2.451</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7963</v>
+        <v>0.5797</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.268</v>
+        <v>-2.451</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6593</v>
+        <v>-1.3235</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7963</v>
+        <v>0.5797</v>
       </c>
       <c r="K20" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4556</v>
+        <v>-0.7437999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>97</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.2428</v>
+        <v>-2.0974</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1752</v>
+        <v>-0.1639</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6505</v>
+        <v>-1.579</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2428</v>
+        <v>-2.0974</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7302</v>
+        <v>-1.2804</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4874</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7302</v>
+        <v>-1.2804</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4196</v>
+        <v>-0.6914</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4874</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="L21" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9321999999999999</v>
+        <v>-1.5084</v>
       </c>
       <c r="N21" t="n">
-        <v>201</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1509,10 +1509,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8867</v>
+        <v>0.8757</v>
       </c>
       <c r="J2" t="n">
-        <v>16.8473</v>
+        <v>16.6383</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7284</v>
+        <v>0.7296</v>
       </c>
       <c r="J3" t="n">
-        <v>13.8396</v>
+        <v>13.8624</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4855</v>
+        <v>0.5008</v>
       </c>
       <c r="J4" t="n">
-        <v>9.224500000000001</v>
+        <v>9.5152</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.27</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3412</v>
+        <v>0.3623</v>
       </c>
       <c r="J5" t="n">
-        <v>6.4828</v>
+        <v>6.8837</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>1.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1385</v>
+        <v>0.1633</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6315</v>
+        <v>3.1027</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>0.75</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2211</v>
+        <v>-0.2488</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.2009</v>
+        <v>-4.7272</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.66</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3148</v>
+        <v>-0.3382</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.9812</v>
+        <v>-6.4258</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.61</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3627</v>
+        <v>-0.3838</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.8913</v>
+        <v>-7.2922</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4064</v>
+        <v>-0.4256</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.7216</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6148</v>
+        <v>-0.6191</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.6812</v>
+        <v>-11.7629</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5113</v>
+        <v>0.5007</v>
       </c>
       <c r="J12" t="n">
-        <v>14.3164</v>
+        <v>14.0196</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4203</v>
+        <v>0.4166</v>
       </c>
       <c r="J13" t="n">
-        <v>11.7684</v>
+        <v>11.6648</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2464</v>
+        <v>0.2525</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8992</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0759</v>
+        <v>-0.0861</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.1252</v>
+        <v>-2.4108</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.506</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.042</v>
+        <v>-14.168</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1938</v>
+        <v>1.2087</v>
       </c>
       <c r="J17" t="n">
-        <v>33.4264</v>
+        <v>33.8436</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3489</v>
+        <v>0.3486</v>
       </c>
       <c r="J18" t="n">
-        <v>9.7692</v>
+        <v>9.7608</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1425</v>
+        <v>0.1539</v>
       </c>
       <c r="J19" t="n">
-        <v>3.99</v>
+        <v>4.3092</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1925</v>
+        <v>-0.1882</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.39</v>
+        <v>-5.2696</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3789</v>
+        <v>-0.3629</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.6092</v>
+        <v>-10.1612</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2436</v>
+        <v>0.2355</v>
       </c>
       <c r="J22" t="n">
-        <v>6.09</v>
+        <v>5.8875</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.93</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.096</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9925</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.115</v>
+        <v>-0.1322</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.875</v>
+        <v>-3.305</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.64</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3704</v>
+        <v>-0.3846</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.26</v>
+        <v>-9.615</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4357</v>
+        <v>-0.4469</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.8925</v>
+        <v>-11.1725</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>2.11</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8664</v>
+        <v>1.8453</v>
       </c>
       <c r="J27" t="n">
-        <v>46.66</v>
+        <v>46.1325</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3202</v>
+        <v>0.3289</v>
       </c>
       <c r="J28" t="n">
-        <v>8.005000000000001</v>
+        <v>8.2225</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2043</v>
+        <v>0.2213</v>
       </c>
       <c r="J29" t="n">
-        <v>5.1075</v>
+        <v>5.5325</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0365</v>
+        <v>0.0601</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9125</v>
+        <v>1.5025</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.385</v>
+        <v>-0.3607</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.625</v>
+        <v>-9.0175</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9666</v>
+        <v>0.9016</v>
       </c>
       <c r="J32" t="n">
-        <v>28.998</v>
+        <v>27.048</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7096</v>
+        <v>0.6726</v>
       </c>
       <c r="J33" t="n">
-        <v>21.288</v>
+        <v>20.178</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1458</v>
+        <v>0.1562</v>
       </c>
       <c r="J34" t="n">
-        <v>4.374</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1538</v>
+        <v>-0.1518</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.614</v>
+        <v>-4.554</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.84</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.542</v>
+        <v>-0.5118</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.26</v>
+        <v>-15.354</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4503</v>
+        <v>0.4422</v>
       </c>
       <c r="J37" t="n">
-        <v>13.509</v>
+        <v>13.266</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.005</v>
+        <v>0.0035</v>
       </c>
       <c r="J38" t="n">
-        <v>0.15</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0476</v>
+        <v>-0.0564</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.428</v>
+        <v>-1.692</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.245</v>
+        <v>-4.659</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2647</v>
+        <v>-0.2786</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.941</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5269</v>
+        <v>0.5183</v>
       </c>
       <c r="J42" t="n">
-        <v>15.807</v>
+        <v>15.549</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1739</v>
+        <v>0.1831</v>
       </c>
       <c r="J43" t="n">
-        <v>5.217</v>
+        <v>5.493</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.111</v>
+        <v>-0.1231</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.33</v>
+        <v>-3.693</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1768</v>
+        <v>-0.1904</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.304</v>
+        <v>-5.712</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2779</v>
+        <v>-0.2909</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.337</v>
+        <v>-8.727</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.289</v>
+        <v>0.3018</v>
       </c>
       <c r="J47" t="n">
-        <v>8.67</v>
+        <v>9.054</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.276</v>
+        <v>0.2891</v>
       </c>
       <c r="J48" t="n">
-        <v>8.279999999999999</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1533</v>
+        <v>0.1673</v>
       </c>
       <c r="J49" t="n">
-        <v>4.599</v>
+        <v>5.019</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1285</v>
+        <v>-0.1397</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.855</v>
+        <v>-4.191</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1617</v>
+        <v>-0.1737</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.851</v>
+        <v>-5.211</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.959</v>
+        <v>0.9031</v>
       </c>
       <c r="J52" t="n">
-        <v>24.934</v>
+        <v>23.4806</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7612</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>19.7912</v>
+        <v>18.8838</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5782</v>
+        <v>0.5628</v>
       </c>
       <c r="J54" t="n">
-        <v>15.0332</v>
+        <v>14.6328</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5542</v>
+        <v>0.5412</v>
       </c>
       <c r="J55" t="n">
-        <v>14.4092</v>
+        <v>14.0712</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3216</v>
+        <v>0.3299</v>
       </c>
       <c r="J56" t="n">
-        <v>8.361599999999999</v>
+        <v>8.577400000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.342</v>
+        <v>0.3316</v>
       </c>
       <c r="J57" t="n">
-        <v>8.891999999999999</v>
+        <v>8.621600000000001</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0716</v>
+        <v>-0.0863</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.8616</v>
+        <v>-2.2438</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1809</v>
+        <v>-0.1985</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.7034</v>
+        <v>-5.161</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2786</v>
+        <v>-0.2953</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.2436</v>
+        <v>-7.6778</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4204</v>
+        <v>-0.4318</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.9304</v>
+        <v>-11.2268</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2155</v>
+        <v>1.17</v>
       </c>
       <c r="J62" t="n">
-        <v>36.465</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3277</v>
+        <v>0.3206</v>
       </c>
       <c r="J63" t="n">
-        <v>9.831</v>
+        <v>9.618</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0898</v>
+        <v>-0.0969</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.694</v>
+        <v>-2.907</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.7</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8673</v>
+        <v>-0.8045</v>
       </c>
       <c r="J65" t="n">
-        <v>-26.019</v>
+        <v>-24.135</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0616</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-31.848</v>
+        <v>-29.169</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5104</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>15.312</v>
+        <v>15.198</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3893</v>
+        <v>0.3941</v>
       </c>
       <c r="J68" t="n">
-        <v>11.679</v>
+        <v>11.823</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3358</v>
+        <v>0.3437</v>
       </c>
       <c r="J69" t="n">
-        <v>10.074</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2057</v>
+        <v>0.2183</v>
       </c>
       <c r="J70" t="n">
-        <v>6.171</v>
+        <v>6.549</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1249</v>
+        <v>-0.1339</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.747</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0087</v>
+        <v>0.9484</v>
       </c>
       <c r="J72" t="n">
-        <v>30.261</v>
+        <v>28.452</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6481</v>
+        <v>0.6206</v>
       </c>
       <c r="J73" t="n">
-        <v>19.443</v>
+        <v>18.618</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4995</v>
+        <v>0.4875</v>
       </c>
       <c r="J74" t="n">
-        <v>14.985</v>
+        <v>14.625</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J75" t="n">
-        <v>1.953</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5523</v>
+        <v>-0.519</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.569</v>
+        <v>-15.57</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6977</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>20.931</v>
+        <v>19.794</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1773</v>
+        <v>0.1755</v>
       </c>
       <c r="J78" t="n">
-        <v>5.319</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2912</v>
+        <v>-0.307</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.736000000000001</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3767</v>
+        <v>-0.3895</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.301</v>
+        <v>-11.685</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4047</v>
+        <v>-0.4163</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.141</v>
+        <v>-12.489</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9129</v>
       </c>
       <c r="J82" t="n">
-        <v>27.4484</v>
+        <v>25.5612</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7035</v>
       </c>
       <c r="J83" t="n">
-        <v>20.93</v>
+        <v>19.698</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1795</v>
+        <v>-0.1792</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.026</v>
+        <v>-5.0176</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4505</v>
+        <v>-0.4311</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.614</v>
+        <v>-12.0708</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5325</v>
+        <v>-0.5051</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.91</v>
+        <v>-14.1428</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7684</v>
+        <v>0.7343</v>
       </c>
       <c r="J87" t="n">
-        <v>21.5152</v>
+        <v>20.5604</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3241</v>
+        <v>0.3268</v>
       </c>
       <c r="J88" t="n">
-        <v>9.0748</v>
+        <v>9.150399999999999</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="J89" t="n">
-        <v>2.5424</v>
+        <v>2.7804</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1782</v>
+        <v>-0.1914</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.9896</v>
+        <v>-5.3592</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4207</v>
+        <v>-0.4289</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.7796</v>
+        <v>-12.0092</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>2.34</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J92" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.62</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2214</v>
+        <v>1.2032</v>
       </c>
       <c r="J93" t="n">
-        <v>21.9852</v>
+        <v>21.6576</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>1.42</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9706</v>
+        <v>0.9276</v>
       </c>
       <c r="J94" t="n">
-        <v>17.4708</v>
+        <v>16.6968</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8154</v>
       </c>
       <c r="J95" t="n">
-        <v>15.2514</v>
+        <v>14.6772</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8254</v>
+        <v>0.7961</v>
       </c>
       <c r="J96" t="n">
-        <v>14.8572</v>
+        <v>14.3298</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.2948</v>
+        <v>-0.3274</v>
       </c>
       <c r="J97" t="n">
-        <v>-5.3064</v>
+        <v>-5.8932</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>0.45</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.4811</v>
+        <v>-0.5</v>
       </c>
       <c r="J98" t="n">
-        <v>-8.659800000000001</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.42</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.136799999999999</v>
+        <v>-9.444599999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.41</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.517</v>
+        <v>-0.5333</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.305999999999999</v>
+        <v>-9.599399999999999</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.33</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.596</v>
+        <v>-0.6055</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.728</v>
+        <v>-10.899</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6279</v>
+        <v>0.6913</v>
       </c>
       <c r="J102" t="n">
-        <v>18.2091</v>
+        <v>20.0477</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5421</v>
+        <v>0.5967</v>
       </c>
       <c r="J103" t="n">
-        <v>15.7209</v>
+        <v>17.3043</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4078</v>
+        <v>0.4443</v>
       </c>
       <c r="J104" t="n">
-        <v>11.8262</v>
+        <v>12.8847</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2975</v>
+        <v>0.2999</v>
       </c>
       <c r="J105" t="n">
-        <v>8.6275</v>
+        <v>8.697100000000001</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.0184</v>
+        <v>-0.9306</v>
       </c>
       <c r="J106" t="n">
-        <v>-29.5336</v>
+        <v>-26.9874</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5634</v>
+        <v>0.6307</v>
       </c>
       <c r="J107" t="n">
-        <v>16.3386</v>
+        <v>18.2903</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5634</v>
+        <v>0.6307</v>
       </c>
       <c r="J108" t="n">
-        <v>16.3386</v>
+        <v>18.2903</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2498</v>
+        <v>0.2598</v>
       </c>
       <c r="J109" t="n">
-        <v>7.2442</v>
+        <v>7.5342</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2073</v>
+        <v>-0.2189</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.0117</v>
+        <v>-6.3481</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3541</v>
+        <v>-0.3635</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.2689</v>
+        <v>-10.5415</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.83</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2423</v>
+        <v>1.3593</v>
       </c>
       <c r="J112" t="n">
-        <v>27.3306</v>
+        <v>29.9046</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4975</v>
+        <v>0.5547</v>
       </c>
       <c r="J113" t="n">
-        <v>10.945</v>
+        <v>12.2034</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4975</v>
+        <v>0.5547</v>
       </c>
       <c r="J114" t="n">
-        <v>10.945</v>
+        <v>12.2034</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3646</v>
+        <v>0.3925</v>
       </c>
       <c r="J115" t="n">
-        <v>8.0212</v>
+        <v>8.635</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3486</v>
+        <v>0.3681</v>
       </c>
       <c r="J116" t="n">
-        <v>7.6692</v>
+        <v>8.0982</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4132</v>
+        <v>0.4411</v>
       </c>
       <c r="J117" t="n">
-        <v>9.090400000000001</v>
+        <v>9.7042</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0505</v>
+        <v>-0.0665</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.111</v>
+        <v>-1.463</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2064</v>
+        <v>-0.225</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.5408</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4422</v>
+        <v>-0.4535</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.728400000000001</v>
+        <v>-9.977</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4793</v>
+        <v>-0.4884</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.5446</v>
+        <v>-10.7448</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3098</v>
+        <v>0.3125</v>
       </c>
       <c r="J122" t="n">
-        <v>10.5332</v>
+        <v>10.625</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J123" t="n">
-        <v>4.8348</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J124" t="n">
-        <v>4.8348</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0349</v>
+        <v>-0.0419</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.1866</v>
+        <v>-1.4246</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3156</v>
+        <v>-0.3279</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.7304</v>
+        <v>-11.1486</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6579</v>
+        <v>0.7267</v>
       </c>
       <c r="J127" t="n">
-        <v>22.3686</v>
+        <v>24.7078</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5606</v>
+        <v>0.6197</v>
       </c>
       <c r="J128" t="n">
-        <v>19.0604</v>
+        <v>21.0698</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1997</v>
+        <v>0.2104</v>
       </c>
       <c r="J129" t="n">
-        <v>6.7898</v>
+        <v>7.1536</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J130" t="n">
-        <v>4.5934</v>
+        <v>5.0626</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0871</v>
+        <v>-0.0819</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.9614</v>
+        <v>-2.7846</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4653</v>
+        <v>0.5164</v>
       </c>
       <c r="J132" t="n">
-        <v>16.2855</v>
+        <v>18.074</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3345</v>
+        <v>0.3418</v>
       </c>
       <c r="J133" t="n">
-        <v>11.7075</v>
+        <v>11.963</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0634</v>
+        <v>0.0716</v>
       </c>
       <c r="J134" t="n">
-        <v>2.219</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0379</v>
+        <v>-0.0442</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.3265</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3481</v>
+        <v>-0.3587</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.1835</v>
+        <v>-12.5545</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5241</v>
+        <v>0.5706</v>
       </c>
       <c r="J137" t="n">
-        <v>18.3435</v>
+        <v>19.971</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0036</v>
+        <v>0.0024</v>
       </c>
       <c r="J138" t="n">
-        <v>0.126</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1597</v>
+        <v>-0.1656</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.5895</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2238</v>
+        <v>-0.2269</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.833</v>
+        <v>-7.9415</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.641</v>
+        <v>-0.6061</v>
       </c>
       <c r="J141" t="n">
-        <v>-22.435</v>
+        <v>-21.2135</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4370/event_4370_evp_summary.xlsx
+++ b/database/event/4370/event_4370_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.9268</v>
+        <v>3.9994</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3068</v>
+        <v>0.3125</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1634</v>
+        <v>1.2161</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9268</v>
+        <v>3.9994</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1647</v>
+        <v>2.1362</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7621</v>
+        <v>1.8632</v>
       </c>
       <c r="H2" t="n">
-        <v>2.248</v>
+        <v>2.1362</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2139</v>
+        <v>1.1994</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7621</v>
+        <v>1.8632</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>2.976</v>
+        <v>3.0626</v>
       </c>
       <c r="N2" t="n">
         <v>273</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5543</v>
+        <v>3.6255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2777</v>
+        <v>0.2833</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9938</v>
+        <v>1.0458</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5543</v>
+        <v>3.6255</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2865</v>
+        <v>2.4154</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2678</v>
+        <v>1.2101</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6499</v>
+        <v>2.6258</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4309</v>
+        <v>1.4743</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2678</v>
+        <v>1.2101</v>
       </c>
       <c r="K3" t="n">
         <v>132</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6987</v>
+        <v>2.6844</v>
       </c>
       <c r="N3" t="n">
         <v>273</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5168</v>
+        <v>3.3623</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2748</v>
+        <v>0.2627</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9767</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5168</v>
+        <v>3.3623</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3862</v>
+        <v>3.3135</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1306</v>
+        <v>0.0488</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2781</v>
+        <v>5.9978</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3901</v>
+        <v>3.3676</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1306</v>
+        <v>0.0488</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5207</v>
+        <v>3.4164</v>
       </c>
       <c r="N4" t="n">
         <v>273</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0141</v>
+        <v>2.9922</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2355</v>
+        <v>0.2338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7479</v>
+        <v>0.7573</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0141</v>
+        <v>2.9922</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4137</v>
+        <v>2.4947</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6004</v>
+        <v>0.4975</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0695</v>
+        <v>2.9234</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6575</v>
+        <v>1.6414</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6004</v>
+        <v>0.4975</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2579</v>
+        <v>2.1389</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9563</v>
+        <v>2.7677</v>
       </c>
       <c r="C6" t="n">
-        <v>0.231</v>
+        <v>0.2163</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7216</v>
+        <v>0.655</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9563</v>
+        <v>2.7677</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1439</v>
+        <v>1.5335</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8124</v>
+        <v>1.2342</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1795</v>
+        <v>1.5335</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1769</v>
+        <v>0.861</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8124</v>
+        <v>1.2342</v>
       </c>
       <c r="K6" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="L6" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9893</v>
+        <v>2.0952</v>
       </c>
       <c r="N6" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9431</v>
+        <v>2.6555</v>
       </c>
       <c r="C7" t="n">
-        <v>0.23</v>
+        <v>0.2075</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7156</v>
+        <v>0.6039</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9431</v>
+        <v>2.6555</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5769</v>
+        <v>3.1422</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3662</v>
+        <v>-0.4867</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5769</v>
+        <v>5.3547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8515</v>
+        <v>3.0065</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3662</v>
+        <v>-0.4867</v>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
         <v>141</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2177</v>
+        <v>2.5198</v>
       </c>
       <c r="N7" t="n">
-        <v>201</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8784</v>
+        <v>2.5819</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2249</v>
+        <v>0.2017</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6861</v>
+        <v>0.5704</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8784</v>
+        <v>2.5819</v>
       </c>
       <c r="F8" t="n">
-        <v>1.743</v>
+        <v>1.5383</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1354</v>
+        <v>1.0436</v>
       </c>
       <c r="H8" t="n">
-        <v>1.743</v>
+        <v>1.5383</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9412</v>
+        <v>0.8637</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1354</v>
+        <v>1.0436</v>
       </c>
       <c r="K8" t="n">
         <v>60</v>
@@ -805,7 +805,7 @@
         <v>141</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0766</v>
+        <v>1.9073</v>
       </c>
       <c r="N8" t="n">
         <v>201</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7052</v>
+        <v>2.5048</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2114</v>
+        <v>0.1957</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6073</v>
+        <v>0.5353</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7052</v>
+        <v>2.5048</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1525</v>
+        <v>1.7606</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4473</v>
+        <v>0.7442</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5069</v>
+        <v>1.7606</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9737</v>
+        <v>0.9885</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4473</v>
+        <v>0.7442</v>
       </c>
       <c r="K9" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L9" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5264</v>
+        <v>1.7327</v>
       </c>
       <c r="N9" t="n">
-        <v>273</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6127</v>
+        <v>2.3724</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2041</v>
+        <v>0.1854</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5652</v>
+        <v>0.475</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6127</v>
+        <v>2.3724</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5637</v>
+        <v>0.3297</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0489</v>
+        <v>2.0427</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5637</v>
+        <v>0.3297</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3044</v>
+        <v>0.1851</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0489</v>
+        <v>2.0427</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3533</v>
+        <v>2.2278</v>
       </c>
       <c r="N10" t="n">
         <v>197</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5645</v>
+        <v>1.7263</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1222</v>
+        <v>0.1349</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1806</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5645</v>
+        <v>1.7263</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2686</v>
+        <v>2.3745</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.6482</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5908</v>
+        <v>2.4723</v>
       </c>
       <c r="I11" t="n">
-        <v>1.399</v>
+        <v>1.3881</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.6482</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>141</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6949000000000001</v>
+        <v>0.7398999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>273</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5288</v>
+        <v>1.3976</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1195</v>
+        <v>0.1092</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0717</v>
+        <v>0.0309</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5288</v>
+        <v>1.3976</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3774</v>
+        <v>0.2623</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1514</v>
+        <v>1.1353</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3774</v>
+        <v>0.2623</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2038</v>
+        <v>0.1473</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1514</v>
+        <v>1.1353</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3552</v>
+        <v>1.2826</v>
       </c>
       <c r="N12" t="n">
         <v>197</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5631</v>
+        <v>0.472</v>
       </c>
       <c r="C13" t="n">
-        <v>0.044</v>
+        <v>0.0369</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3679</v>
+        <v>-0.3908</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5631</v>
+        <v>0.472</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0011</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5642</v>
+        <v>0.5454</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0011</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0412</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5642</v>
+        <v>0.5454</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5636</v>
+        <v>0.5042</v>
       </c>
       <c r="N13" t="n">
         <v>97</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2777</v>
+        <v>0.267</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0217</v>
+        <v>0.0209</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4978</v>
+        <v>-0.4842</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2777</v>
+        <v>0.267</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5769</v>
+        <v>-0.5473</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8546</v>
+        <v>0.8143</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5769</v>
+        <v>-0.5473</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3115</v>
+        <v>-0.3073</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8546</v>
+        <v>0.8143</v>
       </c>
       <c r="K14" t="n">
         <v>146</v>
@@ -1081,7 +1081,7 @@
         <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5431</v>
+        <v>0.507</v>
       </c>
       <c r="N14" t="n">
         <v>197</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3351</v>
+        <v>-0.4178</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0262</v>
+        <v>-0.0326</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7961</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3351</v>
+        <v>-0.4178</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3722</v>
+        <v>-0.8102</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7073</v>
+        <v>0.3924</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3722</v>
+        <v>-0.8102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.201</v>
+        <v>-0.4549</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7073</v>
+        <v>0.3924</v>
       </c>
       <c r="K15" t="n">
         <v>46</v>
@@ -1127,7 +1127,7 @@
         <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5063</v>
+        <v>-0.0625</v>
       </c>
       <c r="N15" t="n">
         <v>97</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3821</v>
+        <v>-0.4322</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0299</v>
+        <v>-0.0338</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7981</v>
+        <v>-0.8027</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3821</v>
+        <v>-0.4322</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4057</v>
+        <v>-0.6846</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4254</v>
+        <v>0.1417</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4057</v>
+        <v>-0.6846</v>
       </c>
       <c r="K16" t="n">
         <v>46</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0197</v>
+        <v>-0.5428999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>97</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.151</v>
+        <v>-1.1701</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0914</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1482</v>
+        <v>-1.1388</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.151</v>
+        <v>-1.1701</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8519</v>
+        <v>-1.781</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7009</v>
+        <v>0.6109</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8519</v>
+        <v>-1.781</v>
       </c>
       <c r="I17" t="n">
         <v>-1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7009</v>
+        <v>0.6109</v>
       </c>
       <c r="K17" t="n">
         <v>46</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2991</v>
+        <v>-0.3891</v>
       </c>
       <c r="N17" t="n">
         <v>97</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.6537</v>
+        <v>-1.5978</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1292</v>
+        <v>-0.1248</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.377</v>
+        <v>-1.3337</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6537</v>
+        <v>-1.5978</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1156</v>
+        <v>-1.0376</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5381</v>
+        <v>-0.5602</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1156</v>
+        <v>-1.0376</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6024</v>
+        <v>-0.5826</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5381</v>
+        <v>-0.5602</v>
       </c>
       <c r="K18" t="n">
         <v>146</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1405</v>
+        <v>-1.1428</v>
       </c>
       <c r="N18" t="n">
         <v>197</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.7507</v>
+        <v>-1.6903</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1368</v>
+        <v>-0.1321</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4212</v>
+        <v>-1.3758</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7507</v>
+        <v>-1.6903</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6524</v>
+        <v>-1.6053</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0983</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6524</v>
+        <v>-1.6053</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8923</v>
+        <v>-0.9013</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0983</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>60</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9905999999999999</v>
+        <v>-0.9863</v>
       </c>
       <c r="N19" t="n">
         <v>201</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.8713</v>
+        <v>-1.7523</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1462</v>
+        <v>-0.1369</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4761</v>
+        <v>-1.404</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8713</v>
+        <v>-1.7523</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.451</v>
+        <v>-2.2402</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5797</v>
+        <v>0.4879</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.451</v>
+        <v>-2.2402</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3235</v>
+        <v>-1.2578</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5797</v>
+        <v>0.4879</v>
       </c>
       <c r="K20" t="n">
         <v>60</v>
@@ -1357,7 +1357,7 @@
         <v>141</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7437999999999999</v>
+        <v>-0.7699</v>
       </c>
       <c r="N20" t="n">
         <v>201</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.0974</v>
+        <v>-1.9978</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1639</v>
+        <v>-0.1561</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.579</v>
+        <v>-1.5159</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0974</v>
+        <v>-1.9978</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2804</v>
+        <v>-1.1999</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2804</v>
+        <v>-1.1999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6914</v>
+        <v>-0.6737</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>46</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5084</v>
+        <v>-1.4716</v>
       </c>
       <c r="N21" t="n">
         <v>97</v>
@@ -1509,10 +1509,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8757</v>
+        <v>0.8057</v>
       </c>
       <c r="J2" t="n">
-        <v>16.6383</v>
+        <v>15.3083</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7296</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>13.8624</v>
+        <v>12.5172</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5008</v>
+        <v>0.4379</v>
       </c>
       <c r="J4" t="n">
-        <v>9.5152</v>
+        <v>8.3201</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>1.27</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3623</v>
+        <v>0.3083</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8837</v>
+        <v>5.8577</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>1.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1633</v>
+        <v>0.1278</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1027</v>
+        <v>2.4282</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>0.75</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2488</v>
+        <v>-0.2343</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.7272</v>
+        <v>-4.4517</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>0.66</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3382</v>
+        <v>-0.329</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.4258</v>
+        <v>-6.251</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.61</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3838</v>
+        <v>-0.3763</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.2922</v>
+        <v>-7.1497</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4256</v>
+        <v>-0.4192</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.086399999999999</v>
+        <v>-7.9648</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6191</v>
+        <v>-0.6334</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.7629</v>
+        <v>-12.0346</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5007</v>
+        <v>0.4417</v>
       </c>
       <c r="J12" t="n">
-        <v>14.0196</v>
+        <v>12.3676</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4166</v>
+        <v>0.3596</v>
       </c>
       <c r="J13" t="n">
-        <v>11.6648</v>
+        <v>10.0688</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2525</v>
+        <v>0.206</v>
       </c>
       <c r="J14" t="n">
-        <v>7.07</v>
+        <v>5.768</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0861</v>
+        <v>-0.0704</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.4108</v>
+        <v>-1.9712</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.506</v>
+        <v>-0.5085</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.168</v>
+        <v>-14.238</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2087</v>
+        <v>1.2273</v>
       </c>
       <c r="J17" t="n">
-        <v>33.8436</v>
+        <v>34.3644</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3486</v>
+        <v>0.311</v>
       </c>
       <c r="J18" t="n">
-        <v>9.7608</v>
+        <v>8.708</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1539</v>
+        <v>0.1282</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3092</v>
+        <v>3.5896</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1882</v>
+        <v>-0.1537</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.2696</v>
+        <v>-4.3036</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3629</v>
+        <v>-0.3204</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.1612</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2355</v>
+        <v>0.194</v>
       </c>
       <c r="J22" t="n">
-        <v>5.8875</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.93</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.096</v>
+        <v>-0.0823</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4</v>
+        <v>-2.0575</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1322</v>
+        <v>-0.1168</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.305</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.64</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3846</v>
+        <v>-0.3718</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.615</v>
+        <v>-9.295</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4469</v>
+        <v>-0.4399</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.1725</v>
+        <v>-10.9975</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>2.11</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J27" t="n">
-        <v>46.1325</v>
+        <v>49.555</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3289</v>
+        <v>0.2965</v>
       </c>
       <c r="J28" t="n">
-        <v>8.2225</v>
+        <v>7.4125</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2213</v>
+        <v>0.1921</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5325</v>
+        <v>4.8025</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0601</v>
+        <v>0.0438</v>
       </c>
       <c r="J30" t="n">
-        <v>1.5025</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3607</v>
+        <v>-0.321</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.0175</v>
+        <v>-8.025</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9016</v>
+        <v>0.8837</v>
       </c>
       <c r="J32" t="n">
-        <v>27.048</v>
+        <v>26.511</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6726</v>
+        <v>0.6379</v>
       </c>
       <c r="J33" t="n">
-        <v>20.178</v>
+        <v>19.137</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1562</v>
+        <v>0.1299</v>
       </c>
       <c r="J34" t="n">
-        <v>4.686</v>
+        <v>3.897</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1518</v>
+        <v>-0.1208</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.554</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.84</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5118</v>
+        <v>-0.4705</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.354</v>
+        <v>-14.115</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4422</v>
+        <v>0.3848</v>
       </c>
       <c r="J37" t="n">
-        <v>13.266</v>
+        <v>11.544</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0035</v>
+        <v>0.0018</v>
       </c>
       <c r="J38" t="n">
-        <v>0.105</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0564</v>
+        <v>-0.0447</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.692</v>
+        <v>-1.341</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.659</v>
+        <v>-4.071</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2786</v>
+        <v>-0.2596</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.358000000000001</v>
+        <v>-7.788</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5183</v>
+        <v>0.5313</v>
       </c>
       <c r="J42" t="n">
-        <v>15.549</v>
+        <v>15.939</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1831</v>
+        <v>0.1661</v>
       </c>
       <c r="J43" t="n">
-        <v>5.493</v>
+        <v>4.983</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1231</v>
+        <v>-0.1047</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.693</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1904</v>
+        <v>-0.1698</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.712</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2909</v>
+        <v>-0.2725</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.727</v>
+        <v>-8.175000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3018</v>
+        <v>0.246</v>
       </c>
       <c r="J47" t="n">
-        <v>9.054</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2891</v>
+        <v>0.2346</v>
       </c>
       <c r="J48" t="n">
-        <v>8.673</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1673</v>
+        <v>0.1284</v>
       </c>
       <c r="J49" t="n">
-        <v>5.019</v>
+        <v>3.852</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1397</v>
+        <v>-0.1201</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.191</v>
+        <v>-3.603</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1737</v>
+        <v>-0.1532</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.211</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9031</v>
+        <v>0.8874</v>
       </c>
       <c r="J52" t="n">
-        <v>23.4806</v>
+        <v>23.0724</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.6996</v>
       </c>
       <c r="J53" t="n">
-        <v>18.8838</v>
+        <v>18.1896</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5628</v>
+        <v>0.5309</v>
       </c>
       <c r="J54" t="n">
-        <v>14.6328</v>
+        <v>13.8034</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5412</v>
+        <v>0.509</v>
       </c>
       <c r="J55" t="n">
-        <v>14.0712</v>
+        <v>13.234</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3299</v>
+        <v>0.2974</v>
       </c>
       <c r="J56" t="n">
-        <v>8.577400000000001</v>
+        <v>7.7324</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3316</v>
+        <v>0.2822</v>
       </c>
       <c r="J57" t="n">
-        <v>8.621600000000001</v>
+        <v>7.3372</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0863</v>
+        <v>-0.0733</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2438</v>
+        <v>-1.9058</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1985</v>
+        <v>-0.1802</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.161</v>
+        <v>-4.6852</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2953</v>
+        <v>-0.2774</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.6778</v>
+        <v>-7.2124</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4318</v>
+        <v>-0.4234</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.2268</v>
+        <v>-11.0084</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.17</v>
+        <v>1.1923</v>
       </c>
       <c r="J62" t="n">
-        <v>35.1</v>
+        <v>35.769</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3206</v>
+        <v>0.2789</v>
       </c>
       <c r="J63" t="n">
-        <v>9.618</v>
+        <v>8.367000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0969</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.907</v>
+        <v>-2.259</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.7</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8045</v>
+        <v>-0.7792</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.135</v>
+        <v>-23.376</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9643</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.169</v>
+        <v>-28.929</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.4481</v>
       </c>
       <c r="J67" t="n">
-        <v>15.198</v>
+        <v>13.443</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.19</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3941</v>
+        <v>0.3401</v>
       </c>
       <c r="J68" t="n">
-        <v>11.823</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3437</v>
+        <v>0.293</v>
       </c>
       <c r="J69" t="n">
-        <v>10.311</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2183</v>
+        <v>0.1792</v>
       </c>
       <c r="J70" t="n">
-        <v>6.549</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1339</v>
+        <v>-0.1147</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.017</v>
+        <v>-3.441</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9484</v>
+        <v>0.9363</v>
       </c>
       <c r="J72" t="n">
-        <v>28.452</v>
+        <v>28.089</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6206</v>
+        <v>0.5848</v>
       </c>
       <c r="J73" t="n">
-        <v>18.618</v>
+        <v>17.544</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4875</v>
+        <v>0.4491</v>
       </c>
       <c r="J74" t="n">
-        <v>14.625</v>
+        <v>13.473</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="J75" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.519</v>
+        <v>-0.4786</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.57</v>
+        <v>-14.358</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.31</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6103</v>
       </c>
       <c r="J77" t="n">
-        <v>19.794</v>
+        <v>18.309</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1755</v>
+        <v>0.138</v>
       </c>
       <c r="J78" t="n">
-        <v>5.265</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.307</v>
+        <v>-0.2894</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.210000000000001</v>
+        <v>-8.682</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3895</v>
+        <v>-0.3773</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.685</v>
+        <v>-11.319</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4163</v>
+        <v>-0.4065</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.489</v>
+        <v>-12.195</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9129</v>
+        <v>0.8968</v>
       </c>
       <c r="J82" t="n">
-        <v>25.5612</v>
+        <v>25.1104</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7035</v>
+        <v>0.6701</v>
       </c>
       <c r="J83" t="n">
-        <v>19.698</v>
+        <v>18.7628</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1792</v>
+        <v>-0.1455</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.0176</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4311</v>
+        <v>-0.3881</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.0708</v>
+        <v>-10.8668</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5051</v>
+        <v>-0.4632</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.1428</v>
+        <v>-12.9696</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7343</v>
+        <v>0.6791</v>
       </c>
       <c r="J87" t="n">
-        <v>20.5604</v>
+        <v>19.0148</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3268</v>
+        <v>0.2744</v>
       </c>
       <c r="J88" t="n">
-        <v>9.150399999999999</v>
+        <v>7.6832</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0993</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>2.7804</v>
+        <v>2.0552</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1914</v>
+        <v>-0.1708</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.3592</v>
+        <v>-4.7824</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4289</v>
+        <v>-0.4218</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.0092</v>
+        <v>-11.8104</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>2.34</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J92" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.62</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2032</v>
+        <v>1.226</v>
       </c>
       <c r="J93" t="n">
-        <v>21.6576</v>
+        <v>22.068</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>1.42</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9276</v>
+        <v>0.9297</v>
       </c>
       <c r="J94" t="n">
-        <v>16.6968</v>
+        <v>16.7346</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8154</v>
+        <v>0.8071</v>
       </c>
       <c r="J95" t="n">
-        <v>14.6772</v>
+        <v>14.5278</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I96" t="n">
-        <v>0.7961</v>
+        <v>0.7863</v>
       </c>
       <c r="J96" t="n">
-        <v>14.3298</v>
+        <v>14.1534</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.3274</v>
+        <v>-0.3156</v>
       </c>
       <c r="J97" t="n">
-        <v>-5.8932</v>
+        <v>-5.6808</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>0.45</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.5</v>
+        <v>-0.5029</v>
       </c>
       <c r="J98" t="n">
-        <v>-9</v>
+        <v>-9.052199999999999</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>0.42</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5283</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.444599999999999</v>
+        <v>-9.509399999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>0.41</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5333</v>
+        <v>-0.5374</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.599399999999999</v>
+        <v>-9.6732</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>0.33</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6055</v>
+        <v>-0.6165</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.899</v>
+        <v>-11.097</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6913</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>20.0477</v>
+        <v>19.6011</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5967</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>17.3043</v>
+        <v>16.9418</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4443</v>
+        <v>0.4081</v>
       </c>
       <c r="J104" t="n">
-        <v>12.8847</v>
+        <v>11.8349</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2999</v>
+        <v>0.2632</v>
       </c>
       <c r="J105" t="n">
-        <v>8.697100000000001</v>
+        <v>7.6328</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9306</v>
+        <v>-0.9207</v>
       </c>
       <c r="J106" t="n">
-        <v>-26.9874</v>
+        <v>-26.7003</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6307</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
-        <v>18.2903</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6307</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
-        <v>18.2903</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2598</v>
+        <v>0.2146</v>
       </c>
       <c r="J109" t="n">
-        <v>7.5342</v>
+        <v>6.2234</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2189</v>
+        <v>-0.1985</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.3481</v>
+        <v>-5.7565</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3635</v>
+        <v>-0.3508</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5415</v>
+        <v>-10.1732</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.83</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3593</v>
+        <v>1.3669</v>
       </c>
       <c r="J112" t="n">
-        <v>29.9046</v>
+        <v>30.0718</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5547</v>
+        <v>0.5511</v>
       </c>
       <c r="J113" t="n">
-        <v>12.2034</v>
+        <v>12.1242</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5547</v>
+        <v>0.5511</v>
       </c>
       <c r="J114" t="n">
-        <v>12.2034</v>
+        <v>12.1242</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3925</v>
+        <v>0.3605</v>
       </c>
       <c r="J115" t="n">
-        <v>8.635</v>
+        <v>7.931</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3681</v>
+        <v>0.3361</v>
       </c>
       <c r="J116" t="n">
-        <v>8.0982</v>
+        <v>7.3942</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4411</v>
+        <v>0.3963</v>
       </c>
       <c r="J117" t="n">
-        <v>9.7042</v>
+        <v>8.7186</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0665</v>
+        <v>-0.0546</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.463</v>
+        <v>-1.2012</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.225</v>
+        <v>-0.2076</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.95</v>
+        <v>-4.5672</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4535</v>
+        <v>-0.4471</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.977</v>
+        <v>-9.8362</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4884</v>
+        <v>-0.4861</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.7448</v>
+        <v>-10.6942</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3125</v>
+        <v>0.2609</v>
       </c>
       <c r="J122" t="n">
-        <v>10.625</v>
+        <v>8.8706</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I123" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J123" t="n">
-        <v>5.1</v>
+        <v>3.9202</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J124" t="n">
-        <v>5.1</v>
+        <v>3.9202</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0419</v>
+        <v>-0.032</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.4246</v>
+        <v>-1.088</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3279</v>
+        <v>-0.3116</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.1486</v>
+        <v>-10.5944</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7267</v>
+        <v>0.7111</v>
       </c>
       <c r="J127" t="n">
-        <v>24.7078</v>
+        <v>24.1774</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.26</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6197</v>
+        <v>0.607</v>
       </c>
       <c r="J128" t="n">
-        <v>21.0698</v>
+        <v>20.638</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2104</v>
+        <v>0.1808</v>
       </c>
       <c r="J129" t="n">
-        <v>7.1536</v>
+        <v>6.1472</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J130" t="n">
-        <v>5.0626</v>
+        <v>4.2194</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0819</v>
+        <v>-0.0612</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.7846</v>
+        <v>-2.0808</v>
       </c>
     </row>
     <row r="132">
@@ -6709,10 +6709,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5164</v>
+        <v>0.4836</v>
       </c>
       <c r="J132" t="n">
-        <v>18.074</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="133">
@@ -6749,10 +6749,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3418</v>
+        <v>0.2886</v>
       </c>
       <c r="J133" t="n">
-        <v>11.963</v>
+        <v>10.101</v>
       </c>
     </row>
     <row r="134">
@@ -6789,10 +6789,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0716</v>
+        <v>0.0517</v>
       </c>
       <c r="J134" t="n">
-        <v>2.506</v>
+        <v>1.8095</v>
       </c>
     </row>
     <row r="135">
@@ -6829,10 +6829,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0442</v>
+        <v>-0.0334</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.547</v>
+        <v>-1.169</v>
       </c>
     </row>
     <row r="136">
@@ -6869,10 +6869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3587</v>
+        <v>-0.345</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.5545</v>
+        <v>-12.075</v>
       </c>
     </row>
     <row r="137">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5706</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>19.971</v>
+        <v>19.565</v>
       </c>
     </row>
     <row r="138">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0024</v>
+        <v>0.0011</v>
       </c>
       <c r="J138" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="139">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1656</v>
+        <v>-0.1352</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.796</v>
+        <v>-4.732</v>
       </c>
     </row>
     <row r="140">
@@ -7029,10 +7029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2269</v>
+        <v>-0.1911</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.9415</v>
+        <v>-6.6885</v>
       </c>
     </row>
     <row r="141">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6061</v>
+        <v>-0.5675</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.2135</v>
+        <v>-19.8625</v>
       </c>
     </row>
   </sheetData>
